--- a/天泰車輛名冊_0908.xlsx
+++ b/天泰車輛名冊_0908.xlsx
@@ -1489,5 +1489,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>